--- a/MU/Test upload format/SHG/2027 - 2028 - SHG/CP1 26-27 SHG .xlsx
+++ b/MU/Test upload format/SHG/2027 - 2028 - SHG/CP1 26-27 SHG .xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
   <si>
     <t>custid</t>
   </si>
@@ -89,46 +89,28 @@
     <t>HomeStay</t>
   </si>
   <si>
-    <t>SHG19</t>
+    <t>Q22728SHG01</t>
+  </si>
+  <si>
+    <t>Q22728SHG03</t>
+  </si>
+  <si>
+    <t>3000</t>
+  </si>
+  <si>
+    <t>IA</t>
+  </si>
+  <si>
+    <t>01-07-2027</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>01-04-2026</t>
-  </si>
-  <si>
-    <t>1000000</t>
+    <t>10000</t>
   </si>
   <si>
     <t>SHG</t>
-  </si>
-  <si>
-    <t>SHG01</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>01-02-2027</t>
-  </si>
-  <si>
-    <t>SHG02</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>SHG03</t>
-  </si>
-  <si>
-    <t>102</t>
   </si>
 </sst>
 </file>
@@ -311,49 +293,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -641,7 +623,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -665,16 +647,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -683,14 +665,14 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -763,9 +745,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -778,11 +759,6 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1104,8 +1080,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="4"/>
+  <dimension ref="A1:T2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="17.8571428571429" customWidth="1"/>
     <col min="2" max="2" width="24.5714285714286" customWidth="1"/>
@@ -1129,58 +1105,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
       <c r="S1" t="s">
@@ -1191,26 +1167,31 @@
       </c>
     </row>
     <row r="2" spans="1:20">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="7">
-        <v>1000</v>
+      <c r="B2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="5"/>
+      <c r="F2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>23</v>
+      <c r="G2" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>25</v>
+      </c>
+      <c r="I2" s="5"/>
+      <c r="J2">
+        <v>1</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -1218,175 +1199,17 @@
       <c r="L2">
         <v>1</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="N2" s="6" t="s">
-        <v>23</v>
-      </c>
       <c r="S2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T2" t="s">
         <v>25</v>
-      </c>
-      <c r="T2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:20">
-      <c r="A3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" s="1">
-        <v>1</v>
-      </c>
-      <c r="K3" s="8">
-        <v>0</v>
-      </c>
-      <c r="L3" s="8">
-        <v>1</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:20">
-      <c r="A4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" s="1">
-        <v>1</v>
-      </c>
-      <c r="K4" s="8">
-        <v>0</v>
-      </c>
-      <c r="L4" s="8">
-        <v>1</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="N4" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S4" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:20">
-      <c r="A5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="1">
-        <v>1</v>
-      </c>
-      <c r="K5" s="8">
-        <v>0</v>
-      </c>
-      <c r="L5" s="8">
-        <v>1</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="S5" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
